--- a/express-backend/utils/uploaded_files/student_list_excel/BSIT_1stYear_A.xlsx
+++ b/express-backend/utils/uploaded_files/student_list_excel/BSIT_1stYear_A.xlsx
@@ -9,14 +9,38 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="CbDOmZEmED9eF3RDzB+nQJZdP2geTVte2x4TwQe+P68="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="69EmprtHmfH46vv5yjavnKEAM2sI34eFyyWtiDYiIA4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="108">
+  <si>
+    <t>Course:</t>
+  </si>
+  <si>
+    <t>Bachelor of Science in Information Technology</t>
+  </si>
+  <si>
+    <t>Academic Year:</t>
+  </si>
+  <si>
+    <t>2025-2026</t>
+  </si>
+  <si>
+    <t>Section:</t>
+  </si>
+  <si>
+    <t>BSIT11A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Term: </t>
+  </si>
+  <si>
+    <t>1st Semester</t>
+  </si>
   <si>
     <t>Student ID</t>
   </si>
@@ -33,6 +57,9 @@
     <t>Section</t>
   </si>
   <si>
+    <t>Gender</t>
+  </si>
+  <si>
     <t>Contact Number</t>
   </si>
   <si>
@@ -57,448 +84,286 @@
     <t>A</t>
   </si>
   <si>
-    <t>09142413168</t>
+    <t>F</t>
   </si>
   <si>
     <t>Roberto Flores</t>
   </si>
   <si>
-    <t>09096098938</t>
-  </si>
-  <si>
     <t>PDM-2025-001337</t>
   </si>
   <si>
     <t>Angela Ramos</t>
   </si>
   <si>
-    <t>09531374565</t>
-  </si>
-  <si>
     <t>Daniel Villanueva</t>
   </si>
   <si>
-    <t>09093621434</t>
-  </si>
-  <si>
     <t>PDM-2025-001338</t>
   </si>
   <si>
     <t>Angela Garcia</t>
   </si>
   <si>
-    <t>09272973348</t>
-  </si>
-  <si>
     <t>Ramon Torres</t>
   </si>
   <si>
-    <t>09415390350</t>
-  </si>
-  <si>
     <t>PDM-2025-001339</t>
   </si>
   <si>
     <t>Jose Ramos</t>
   </si>
   <si>
-    <t>09320256688</t>
+    <t>M</t>
   </si>
   <si>
     <t>Patricia Cruz</t>
   </si>
   <si>
-    <t>09752716598</t>
-  </si>
-  <si>
     <t>PDM-2025-001340</t>
   </si>
   <si>
     <t>Carlo Villanueva</t>
   </si>
   <si>
-    <t>09406528266</t>
-  </si>
-  <si>
     <t>Ramon Reyes</t>
   </si>
   <si>
-    <t>09167000013</t>
-  </si>
-  <si>
     <t>PDM-2025-001341</t>
   </si>
   <si>
     <t>Ana Bautista</t>
   </si>
   <si>
-    <t>09576403909</t>
-  </si>
-  <si>
     <t>Carmen Bautista</t>
   </si>
   <si>
-    <t>09236090891</t>
-  </si>
-  <si>
     <t>PDM-2025-001342</t>
   </si>
   <si>
     <t>Pedro Torres</t>
   </si>
   <si>
-    <t>09214931682</t>
-  </si>
-  <si>
     <t>Roberto Garcia</t>
   </si>
   <si>
-    <t>09619594063</t>
-  </si>
-  <si>
     <t>PDM-2025-001343</t>
   </si>
   <si>
     <t>Catherine Torres</t>
   </si>
   <si>
-    <t>09035474266</t>
-  </si>
-  <si>
     <t>Roberto Castro</t>
   </si>
   <si>
-    <t>09953018873</t>
-  </si>
-  <si>
     <t>PDM-2025-001344</t>
   </si>
   <si>
     <t>Sophia Reyes</t>
   </si>
   <si>
-    <t>09733675499</t>
-  </si>
-  <si>
     <t>Antonio Flores</t>
   </si>
   <si>
-    <t>09296000542</t>
-  </si>
-  <si>
     <t>PDM-2025-001345</t>
   </si>
   <si>
     <t>Miguel Reyes</t>
   </si>
   <si>
-    <t>09204527087</t>
-  </si>
-  <si>
     <t>Antonio Ramos</t>
   </si>
   <si>
-    <t>09478646252</t>
-  </si>
-  <si>
     <t>PDM-2025-001346</t>
   </si>
   <si>
     <t>Catherine Castro</t>
   </si>
   <si>
-    <t>09427806207</t>
-  </si>
-  <si>
     <t>Gloria Castro</t>
   </si>
   <si>
-    <t>09405418421</t>
-  </si>
-  <si>
     <t>PDM-2025-001347</t>
   </si>
   <si>
     <t>Juan Castro</t>
   </si>
   <si>
-    <t>09868342721</t>
-  </si>
-  <si>
     <t>Patricia Santos</t>
   </si>
   <si>
-    <t>09697954340</t>
-  </si>
-  <si>
     <t>PDM-2025-001348</t>
   </si>
   <si>
     <t>Maria Villanueva</t>
   </si>
   <si>
-    <t>09689877414</t>
-  </si>
-  <si>
     <t>Roberto Ramos</t>
   </si>
   <si>
-    <t>09792894131</t>
-  </si>
-  <si>
     <t>PDM-2025-001349</t>
   </si>
   <si>
-    <t>09504734177</t>
-  </si>
-  <si>
     <t>Alberto Mendoza</t>
   </si>
   <si>
-    <t>09906410598</t>
-  </si>
-  <si>
     <t>PDM-2025-001350</t>
   </si>
   <si>
     <t>Carlo Flores</t>
   </si>
   <si>
-    <t>09600835895</t>
-  </si>
-  <si>
     <t>Roberto Mendoza</t>
   </si>
   <si>
-    <t>09031969840</t>
-  </si>
-  <si>
     <t>PDM-2025-001351</t>
   </si>
   <si>
     <t>Miguel Flores</t>
   </si>
   <si>
-    <t>09148789591</t>
-  </si>
-  <si>
     <t>Fernando Cruz</t>
   </si>
   <si>
-    <t>09417099022</t>
-  </si>
-  <si>
     <t>PDM-2025-001352</t>
   </si>
   <si>
     <t>Juan Villanueva</t>
   </si>
   <si>
-    <t>09623868338</t>
-  </si>
-  <si>
     <t>Antonio Torres</t>
   </si>
   <si>
-    <t>09703850023</t>
-  </si>
-  <si>
     <t>PDM-2025-001353</t>
   </si>
   <si>
-    <t>09017332158</t>
-  </si>
-  <si>
-    <t>09331692214</t>
-  </si>
-  <si>
     <t>PDM-2025-001354</t>
   </si>
   <si>
     <t>Mark Garcia</t>
   </si>
   <si>
-    <t>09614411509</t>
-  </si>
-  <si>
     <t>Roberto Cruz</t>
   </si>
   <si>
-    <t>09865544628</t>
-  </si>
-  <si>
     <t>PDM-2025-001355</t>
   </si>
   <si>
     <t>Mark Bautista</t>
   </si>
   <si>
-    <t>09681502410</t>
-  </si>
-  <si>
     <t>Daniel Reyes</t>
   </si>
   <si>
-    <t>09234214560</t>
-  </si>
-  <si>
     <t>PDM-2025-001356</t>
   </si>
   <si>
     <t>Carlo Santos</t>
   </si>
   <si>
-    <t>09023904269</t>
-  </si>
-  <si>
     <t>Fernando Garcia</t>
   </si>
   <si>
-    <t>09815697351</t>
-  </si>
-  <si>
     <t>PDM-2025-001357</t>
   </si>
   <si>
     <t>Mark Mendoza</t>
   </si>
   <si>
-    <t>09711320301</t>
-  </si>
-  <si>
     <t>Lucia Santos</t>
   </si>
   <si>
-    <t>09364395972</t>
-  </si>
-  <si>
     <t>PDM-2025-001358</t>
   </si>
   <si>
     <t>Maria Bautista</t>
   </si>
   <si>
-    <t>09271512129</t>
-  </si>
-  <si>
     <t>Teresa Ramos</t>
   </si>
   <si>
-    <t>09582553727</t>
-  </si>
-  <si>
     <t>PDM-2025-001359</t>
   </si>
   <si>
     <t>Paolo Torres</t>
   </si>
   <si>
-    <t>09516120757</t>
-  </si>
-  <si>
     <t>Alberto Flores</t>
   </si>
   <si>
-    <t>09482830334</t>
-  </si>
-  <si>
     <t>PDM-2025-001360</t>
   </si>
   <si>
     <t>Elena Torres</t>
   </si>
   <si>
-    <t>09718018363</t>
-  </si>
-  <si>
     <t>Teresa Villanueva</t>
   </si>
   <si>
-    <t>09458346558</t>
-  </si>
-  <si>
     <t>PDM-2025-001361</t>
   </si>
   <si>
     <t>Elena Cruz</t>
   </si>
   <si>
-    <t>09449860210</t>
-  </si>
-  <si>
     <t>Patricia Flores</t>
   </si>
   <si>
-    <t>09988791478</t>
-  </si>
-  <si>
     <t>PDM-2025-001362</t>
   </si>
   <si>
     <t>Rosa Bautista</t>
   </si>
   <si>
-    <t>09595330808</t>
-  </si>
-  <si>
     <t>Patricia Bautista</t>
   </si>
   <si>
-    <t>09139523199</t>
-  </si>
-  <si>
     <t>PDM-2025-001363</t>
   </si>
   <si>
     <t>Ana Flores</t>
   </si>
   <si>
-    <t>09380184337</t>
-  </si>
-  <si>
     <t>Teresa Santos</t>
   </si>
   <si>
-    <t>09584096171</t>
-  </si>
-  <si>
     <t>PDM-2025-001364</t>
   </si>
   <si>
     <t>Maria Ramos</t>
   </si>
   <si>
-    <t>09283861630</t>
-  </si>
-  <si>
     <t>Roberto Santos</t>
   </si>
   <si>
-    <t>09424473705</t>
-  </si>
-  <si>
     <t>PDM-2025-001365</t>
   </si>
   <si>
     <t>Miguel Santos</t>
-  </si>
-  <si>
-    <t>09858976615</t>
-  </si>
-  <si>
-    <t>09990700840</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -507,9 +372,9 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -520,37 +385,99 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border/>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -580,40 +507,40 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow"/>
+        <a:ea typeface="Aptos Narrow"/>
+        <a:cs typeface="Aptos Narrow"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow"/>
+        <a:ea typeface="Aptos Narrow"/>
+        <a:cs typeface="Aptos Narrow"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -762,15 +689,18 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.86"/>
-    <col customWidth="1" min="2" max="2" width="19.0"/>
-    <col customWidth="1" min="3" max="5" width="9.0"/>
-    <col customWidth="1" min="6" max="6" width="17.86"/>
-    <col customWidth="1" min="7" max="7" width="21.71"/>
-    <col customWidth="1" min="8" max="8" width="26.14"/>
-    <col customWidth="1" min="9" max="26" width="9.0"/>
+    <col customWidth="1" min="1" max="1" width="18.13"/>
+    <col customWidth="1" min="2" max="2" width="43.25"/>
+    <col customWidth="1" min="3" max="3" width="8.63"/>
+    <col customWidth="1" min="4" max="4" width="15.88"/>
+    <col customWidth="1" min="5" max="5" width="13.75"/>
+    <col customWidth="1" min="6" max="6" width="8.63"/>
+    <col customWidth="1" min="7" max="7" width="17.0"/>
+    <col customWidth="1" min="8" max="8" width="17.13"/>
+    <col customWidth="1" min="9" max="9" width="25.25"/>
+    <col customWidth="1" min="10" max="26" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -780,807 +710,928 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="3" ht="29.25" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="I3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="6">
+        <v>9.142413168E9</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="I4" s="6">
+        <v>9.096098938E9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="C5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="6">
+        <v>9.531374565E9</v>
+      </c>
+      <c r="H5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="I5" s="6">
+        <v>9.093621434E9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="B6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="C6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="6">
+        <v>9.272973348E9</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I6" s="6">
+        <v>9.41539035E9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="B7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G7" s="6">
+        <v>9.320256688E9</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="I7" s="6">
+        <v>9.752716598E9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="C8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="6">
+        <v>9.406528266E9</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="I8" s="6">
+        <v>9.167000013E9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="C9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="6">
+        <v>9.576403909E9</v>
+      </c>
+      <c r="H9" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I9" s="6">
+        <v>9.236090891E9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="B10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="6">
+        <v>9.214931682E9</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="I10" s="6">
+        <v>9.619594063E9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="C11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="6">
+        <v>9.035474266E9</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="I11" s="6">
+        <v>9.953018873E9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="C12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="6">
+        <v>9.733675499E9</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="I12" s="6">
+        <v>9.296000542E9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="C13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="6">
+        <v>9.204527087E9</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="I13" s="6">
+        <v>9.478646252E9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="C14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="6">
+        <v>9.427806207E9</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="I14" s="6">
+        <v>9.405418421E9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="B15" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="6">
+        <v>9.868342721E9</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="I15" s="6">
+        <v>9.69795434E9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="C16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="6">
+        <v>9.689877414E9</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="I16" s="6">
+        <v>9.792894131E9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B17" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="6">
+        <v>9.504734177E9</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="I17" s="6">
+        <v>9.906410598E9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="C18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="6">
+        <v>9.600835895E9</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="I18" s="6">
+        <v>9.03196984E9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B19" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="C19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="6">
+        <v>9.148789591E9</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="I19" s="6">
+        <v>9.417099022E9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="B20" s="6" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="C20" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="6">
+        <v>9.623868338E9</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="I20" s="6">
+        <v>9.703850023E9</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="B21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="6">
+        <v>9.017332158E9</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I21" s="6">
+        <v>9.331692214E9</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="B22" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="C22" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="6">
+        <v>9.614411509E9</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
+      <c r="I22" s="6">
+        <v>9.865544628E9</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="B23" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="C23" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="6">
+        <v>9.68150241E9</v>
+      </c>
+      <c r="H23" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="I23" s="6">
+        <v>9.23421456E9</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="6" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
+      <c r="B24" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C24" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="6">
+        <v>9.023904269E9</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="I24" s="6">
+        <v>9.815697351E9</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="B25" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="C25" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="6">
+        <v>9.711320301E9</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
+      <c r="I25" s="6">
+        <v>9.364395972E9</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B26" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="C26" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="6">
+        <v>9.271512129E9</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="I26" s="6">
+        <v>9.582553727E9</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="B27" s="6" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
+      <c r="C27" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" s="6">
+        <v>9.516120757E9</v>
+      </c>
+      <c r="H27" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="I27" s="6">
+        <v>9.482830334E9</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="B28" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="C28" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="6">
+        <v>9.718018363E9</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="I28" s="6">
+        <v>9.458346558E9</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="6" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
+      <c r="B29" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="C29" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="6">
+        <v>9.44986021E9</v>
+      </c>
+      <c r="H29" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H19" s="3" t="s">
+      <c r="I29" s="6">
+        <v>9.988791478E9</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="6" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
+      <c r="B30" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C30" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="6">
+        <v>9.595330808E9</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="I30" s="6">
+        <v>9.139523199E9</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="B31" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="C31" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="6">
+        <v>9.380184337E9</v>
+      </c>
+      <c r="H31" s="6" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
+      <c r="I31" s="6">
+        <v>9.584096171E9</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B32" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="C32" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="6">
+        <v>9.28386163E9</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="I32" s="6">
+        <v>9.424473705E9</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="B33" s="6" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
+      <c r="C33" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" s="6">
+        <v>9.858976615E9</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I33" s="6">
+        <v>9.99070084E9</v>
+      </c>
+    </row>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
     <row r="36" ht="15.75" customHeight="1"/>
